--- a/TestData/TestBlob.xlsx
+++ b/TestData/TestBlob.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="AA5" s="0" t="n">
         <f aca="false">((3*Y$7^2*Z$7*G5)/(4*PI()))^(1/3)</f>
-        <v>2.80071652906799</v>
+        <v>2.800716529068</v>
       </c>
       <c r="AB5" s="0" t="n">
         <v>-0.380768</v>
